--- a/order_processor/output/K-05-002.xlsx
+++ b/order_processor/output/K-05-002.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -607,7 +607,7 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -683,7 +683,7 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -759,7 +759,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -835,7 +835,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -911,7 +911,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -944,7 +944,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1063,7 +1063,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1139,7 +1139,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1215,7 +1215,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1367,7 +1367,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1519,7 +1519,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1595,7 +1595,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
